--- a/光伏配储项目/电价数据/2026/河源站.xlsx
+++ b/光伏配储项目/电价数据/2026/河源站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.48594</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75581</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5444600000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5579400000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.48687</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.47912</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.41735</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.41397</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.40358</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.43044</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47349</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.15805</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.23915</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.21765</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.0205</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.07820999999999999</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.04413</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.15908</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.16292</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.14845</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.10293</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.0057</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5168200000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5353</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7339199999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.11934</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.17489</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43156</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43779</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6611699999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.86185</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47049</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.19304</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.45662</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.31287</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.99288</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.27851</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.52461</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.67963</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.72992</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.09636</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.96129</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.89158</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80032</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.76117</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51498</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48335</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46521</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42748</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71688</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.88852</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.94111</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50226</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52459</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5092300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5093799999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49136</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47287</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.42667</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.40539</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.44513</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.14307</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.00175</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.06467</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.49052</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.4863</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50442</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.13925</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.25978</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.00197</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.05257</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.5689099999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.02047</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.00847</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.6929099999999999</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.62695</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.02441</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.02475</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.10213</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.8062999999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.26818</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.16834</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.26026</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.25708</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.27099</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.42678</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.58043</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5957899999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7453500000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7567</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.16103</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24802</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13508</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.83872</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20493</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10588</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25641</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02312</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.09017</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.65077</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98307</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.91339</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.95839</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7841</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.89202</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.73982</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.77787</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.73084</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.76291</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45104</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33492</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51297</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49289</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48986</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44517</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43148</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44753</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47758</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44636</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44153</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.51569</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>1.40843</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22301</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.53608</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.55264</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.22486</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7824800000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.48399</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.42332</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42984</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43397</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.43092</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.51452</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.48673</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28445</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6208899999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.64328</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46591</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50604</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.47204</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5526599999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.49202</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.61329</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48421</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6173099999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.5756599999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.55775</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7200700000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.60442</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5209400000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.42064</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.5563899999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43477</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45848</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34233</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.50243</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43967</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45222</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.4199</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43092</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.10529</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.07143000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.15441</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.06479</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56555</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.17566</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.16825</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.15052</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6227999999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.44662</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40624</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28217</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50876</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45108</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.4668</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40196</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47494</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.48815</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.5507000000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43948</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55765</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49294</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46821</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50436</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42631</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32123</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.11743</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27262</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.08544</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.27003</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.16278</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.10479</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13363</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.11351</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04744</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.02598</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.18028</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.17953</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.05638</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.00544</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.01705</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.24318</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.41856</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.41948</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.41722</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.43037</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42273</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43596</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.48535</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41372</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.42255</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.54388</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37044</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.84636</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.5645800000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5248700000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.53742</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.4253</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.5953999999999999</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.40787</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10218</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.006160000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19885</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26456</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.15671</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03007</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05118</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34676</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32313</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.43001</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42898</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78546</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88747</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86912</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.57048</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.54089</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62182</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41997</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38904</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45416</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4548</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.42109</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.44516</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.66331</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.49934</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.62615</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.8108200000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.88387</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47106</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4923</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.6620900000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.49613</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.03759</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.7925399999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8736499999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.5111600000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.89188</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.82938</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5911000000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47229</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.47629</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5353</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.47986</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.44139</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.42407</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.37075</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9351</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.52507</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.47318</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45417</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54702</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.42103</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.46593</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.46304</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.6070800000000001</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.44021</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.22661</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.09584999999999999</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.26929</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26836</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20068</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.44045</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25842</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27948</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.52865</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42752</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.47273</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4735</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.45922</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.46075</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.77235</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.42774</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.94424</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.4822</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.19996</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.72825</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.82011</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.67938</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.79028</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.58833</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47473</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5257200000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46345</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.49423</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.43867</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.47534</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.6077</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45628</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.48027</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.40869</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.50895</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.54387</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.5167999999999999</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.46449</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.5063299999999999</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.47039</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.51603</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.45262</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.62593</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.54459</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25159</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15745</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27575</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01608</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26422</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25877</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.41093</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.6479</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.54357</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.01115</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.54979</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.51703</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.50843</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.42822</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.36721</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.44451</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.40724</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.40983</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.41129</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.40436</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.42109</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.42082</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.52886</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.40296</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.50839</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.53907</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.43802</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.52177</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.48872</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.43887</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.47702</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21543</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.07707</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1182</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.09484999999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26438</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.23154</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.09087999999999999</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25598</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13329</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05824</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.03516</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.06864000000000001</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.06193</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16424</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.08019</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.45203</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.43655</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.53888</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4602</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.44368</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.46314</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.45373</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.5385800000000001</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.52488</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.52106</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.5275299999999999</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.46119</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.40233</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.38806</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.67138</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.40602</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.56125</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.49088</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.47946</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.42797</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.42491</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.40923</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.4288</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.53777</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.4142</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.42724</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.26647</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26725</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23909</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.17812</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.22916</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21682</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.18078</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.22945</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27592</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25581</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.95941</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.40374</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.51506</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41779</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40425</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.47013</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.42905</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.39251</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.6251</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.63286</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.42082</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.41841</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.43294</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.41768</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.39707</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.45025</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.14073</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6789500000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.51209</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.45801</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46303</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.4215</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25779</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2737</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.18739</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.10371</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.24003</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.5700499999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27821</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.28693</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.07231</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43371</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.58417</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47918</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46433</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44585</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7179</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.03536</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8844</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.71585</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52728</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26816</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.64944</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.41971</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.51135</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42722</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.42938</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.40933</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.42739</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.41346</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.41739</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.45868</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.43102</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.42944</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.40569</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.46879</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.42666</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38608</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.42018</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.42201</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.45513</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.44258</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.49992</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.45169</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.46014</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.36729</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.5812200000000001</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41891</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.48698</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43342</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.41414</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39342</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6736599999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.05929</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.51898</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.54087</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.45299</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.37214</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.42928</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.37813</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.42168</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26068</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.11003</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.21966</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.13134</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.2056</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.23693</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.23871</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.25415</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.15884</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.21991</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2508</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.40828</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.42301</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.4627</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.55577</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.49636</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.67798</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6355700000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.65246</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.6377200000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84573</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.6123500000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.17204</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.65461</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.52179</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.59727</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.49944</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.48138</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.41397</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.38794</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.58497</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.7181900000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.62491</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.8924800000000001</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.47459</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.47631</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.45234</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4663</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.45998</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.47444</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.44537</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.45632</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.45376</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.48405</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.43509</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.48116</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.43896</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.46769</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.45805</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.47386</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.46278</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.55192</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.5406299999999999</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.72015</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.6161599999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5345299999999999</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.6057100000000001</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.5307200000000001</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46565</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41157</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43259</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46924</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46961</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.54991</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45229</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.41654</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.46676</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.44609</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43109</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.64762</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.9379299999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.49954</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.5286900000000001</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.50501</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.41368</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.43496</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.50388</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.5916399999999999</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.53163</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.6293800000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.63163</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.69599</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.93424</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.15534</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.27054</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.91567</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.08424</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.9044800000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.68692</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.12614</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78726</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.64077</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6900599999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.55531</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.5842000000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.58161</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.5702200000000001</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.56201</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.47426</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.68652</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.49188</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.5141699999999999</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5382899999999999</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45213</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44207</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.52354</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.4338</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.56832</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.46388</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.47274</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.43277</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.60334</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.45246</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.45441</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.43891</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40442</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.26205</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.40938</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.22554</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.43885</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.51347</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.6321</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.009310000000000001</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.11128</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.04411</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.42877</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.44183</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.48623</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.46346</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.45302</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43517</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.51834</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42574</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.46355</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.48607</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.49667</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.51263</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.49207</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.45939</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.47048</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.43044</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4671</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.5016700000000001</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.47616</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.51924</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.50015</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.45969</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.61686</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.4719100000000001</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.48718</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.49177</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.45492</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.47518</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.46042</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.60793</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.57796</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.57221</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.46006</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.58531</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.43383</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.45945</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.54792</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.44724</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.42676</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.44121</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.44759</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.45397</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.5330900000000001</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.53134</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.54647</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.4859</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.41701</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.5461699999999999</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.21177</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.21363</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.42507</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.23085</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.06897</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27084</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.09479000000000001</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.11407</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.18605</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22542</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21548</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.44325</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.44893</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.40777</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44664</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.46786</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.49125</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.43903</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.48044</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.49535</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.45513</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.45576</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.42004</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.50285</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.49408</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.46896</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.50442</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.49628</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.49628</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.49021</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.49021</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.49384</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.49703</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.49021</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.4908</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.50471</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.50428</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.5079399999999999</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.39601</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.03249</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0008399999999999999</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15122</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02267</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01491</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04307</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04101</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04829</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02946</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03866</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00143</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27881</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03639</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03562</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20539</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26865</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.41849</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.53283</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.40502</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.15979</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.99405</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.48693</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.8497899999999999</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.51815</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.53326</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5844199999999999</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.44592</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.49895</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.46138</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.47434</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.46877</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.61661</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.45579</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.42991</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.63842</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.55106</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.62885</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.5766</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.63178</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.59953</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.58469</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.60876</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.64955</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46379</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.5280499999999999</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.41027</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.51244</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.45666</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.37435</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.90872</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87091</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.41394</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.48629</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02843</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.01906</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.00827</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.7577200000000001</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.6448400000000001</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04555</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.0307</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04040999999999999</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.02645</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.04278</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.02975</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25443</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.39784</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.42499</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.44661</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.03048</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.13128</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.09304</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.99938</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.11821</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.03506</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.12731</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.86165</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8599</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.86405</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.96089</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.12006</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.12329</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.11485</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.41897</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.41881</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.59682</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8766900000000001</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.42104</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.82328</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.51742</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.61437</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.51271</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.5124099999999999</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40466</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.48018</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.5208200000000001</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.40651</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.65611</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.43964</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.4633</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.45059</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.60064</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.52561</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.49774</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.49754</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.6071799999999999</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.6609299999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.48921</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.51573</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.15445</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40196</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.03008</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.04661999999999999</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.005679999999999999</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.20236</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.44072</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.47898</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26095</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.42746</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.44969</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.61974</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.21615</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.50176</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.89659</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.60462</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.54083</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.53167</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.48363</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.66506</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3999</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.49378</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.5099399999999999</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.48075</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.45142</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.44556</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.43962</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.41463</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.40506</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40523</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.54092</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.43341</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.84163</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.9992300000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.82217</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.24897</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.76301</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.58775</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.40623</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42609</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41048</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.96562</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8305</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46689</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.46436</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.57377</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.55606</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6480399999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.81735</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5659099999999999</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.91335</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.79483</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.6035</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.46081</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.53267</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.5334500000000001</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.44546</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.44508</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.40024</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.43959</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.44755</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.43487</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.42405</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.38779</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.41316</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.40468</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.41058</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.45613</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38827</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.39891</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43103</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41081</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.45232</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.47662</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.66626</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.64935</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.7728400000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5421699999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.7688700000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.46782</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.9365599999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.44256</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.00289</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.47556</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.49214</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.43561</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.40446</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.45323</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.5930800000000001</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.41569</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.38874</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17861</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27266</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.17512</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.21026</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.09698999999999999</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.17731</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.00454</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.05853</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26522</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.01876</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05047</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04972</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.11255</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03952000000000001</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.009630000000000001</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.23319</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.18423</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20891</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39123</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.54172</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.45547</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.51558</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47243</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43673</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42406</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.44404</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.47641</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40636</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.41627</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.24274</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.12286</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.25015</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.41608</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.41359</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.40831</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.40426</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.40284</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.41474</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40481</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.23169</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.26496</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.27814</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.04289</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.08698</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27846</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.41629</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.43043</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.43103</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40575</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41392</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.41943</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42461</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.41764</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38752</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.47894</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.41083</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.45006</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40294</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39506</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.38427</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17674</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14638</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19956</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.01309</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.24578</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.02954</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.01639</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.01644</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.00326</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.00323</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13731</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.02744</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.08009999999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18124</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.00941</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.23169</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27192</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16546</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26861</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.01189</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.23058</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.05546</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20366</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14756</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25848</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.41363</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.42752</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.41817</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.42514</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.42791</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.41818</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42958</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.50787</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41818</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41522</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40859</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.40722</v>
       </c>
     </row>
   </sheetData>
